--- a/artfynd/A 32762-2021 artfynd.xlsx
+++ b/artfynd/A 32762-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 32762-2021 artfynd.xlsx
+++ b/artfynd/A 32762-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,64 +675,51 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>95982443</v>
+        <v>98712062</v>
       </c>
       <c r="B2" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>6456</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Årjäng, Vrm</t>
+          <t>Norr Abborrtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>335020.9334444987</v>
+        <v>334814</v>
       </c>
       <c r="R2" t="n">
-        <v>6606460.846465609</v>
+        <v>6606444</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -756,22 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,55 +757,51 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mikael Schulin</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mikael Schulin</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>98711976</v>
+        <v>98711978</v>
       </c>
       <c r="B3" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -841,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>334382.3738184216</v>
+        <v>334382</v>
       </c>
       <c r="R3" t="n">
-        <v>6606377.348672673</v>
+        <v>6606377</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,19 +847,9 @@
           <t>2021-09-28</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-09-28</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,15 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>98711978</v>
+        <v>98711992</v>
       </c>
       <c r="B4" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -957,10 +915,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>334382.3738184216</v>
+        <v>334382</v>
       </c>
       <c r="R4" t="n">
-        <v>6606377.348672673</v>
+        <v>6606391</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,19 +948,9 @@
           <t>2021-09-28</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-09-28</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,37 +978,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>98712062</v>
+        <v>98712014</v>
       </c>
       <c r="B5" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1073,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>334813.2725699538</v>
+        <v>334395</v>
       </c>
       <c r="R5" t="n">
-        <v>6606443.091462617</v>
+        <v>6606400</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1106,19 +1049,14 @@
           <t>2021-09-28</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-09-28</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På två aspar</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,6 +1081,225 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>95982443</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Årjäng, Vrm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>335021</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6606461</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Karlanda</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2021-09-08</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2021-09-08</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Mikael Schulin</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Mikael Schulin</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>98711976</v>
+      </c>
+      <c r="B7" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Norr Abborrtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>334382</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6606377</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Karlanda</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2021-09-28</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2021-09-28</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
